--- a/fixtures/indice_minimo.xlsx
+++ b/fixtures/indice_minimo.xlsx
@@ -476,13 +476,13 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>bien_formado.html</t>
+          <t>bien_formado.txt</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TXT</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>informe.html</t>
+          <t>informe.txt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TXT</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>informe.html</t>
+          <t>informe.txt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TXT</t>
         </is>
       </c>
     </row>
@@ -583,13 +583,13 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>anidado.html</t>
+          <t>anidado.txt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TXT</t>
         </is>
       </c>
     </row>
